--- a/stories/arbres/ATOM-REL.AMI.001-10.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-10.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Clémence est au parc. Papa est au banc. Clémence a des craies. Les craies sont colorées. Nora arrive près du muret. Clémence veut jouer. Papa dit : tu peux inviter. Inviter, c'est demander. Clémence dit : tu veux jouer avec nous ? Nora secoue la tête. Nora dit : non. Clémence a le ventre un peu serré. Papa s'approche. Papa dit : on peut accepter un non. Accepter un non, c'est possible. Clémence dit : d'accord. Elle dessine avec papa. Nora joue au cerceau. Clémence n'insiste pas. Papa dit : merci. Tu as su inviter. Tu as su accepter un non.</t>
+          <t>Clémence est au parc. Papa est au banc. Clémence a des craies. Les craies sont colorées. Nora arrive près du muret. Clémence veut jouer. Tu peux inviter. Inviter, c'est demander. Tu veux jouer avec nous ? Nora secoue la tête. Non. Clémence a le ventre un peu serré. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. D'accord. Elle dessine avec papa. Nora joue au cerceau. Clémence n'insiste pas. Merci. Tu as su inviter. Tu as su accepter un non.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,20 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Clémence est au parc. Papa est au banc. Clémence a des craies. Les craies sont colorées. Nora arrive près du muret. Clémence veut jouer.
+papa|Tu peux inviter. Inviter, c'est demander.
+enfant-f|Tu veux jouer avec nous ?
+narrateur|Nora secoue la tête.
+copine|Non.
+narrateur|Clémence a le ventre un peu serré. Papa s'approche.
+papa|On peut accepter un non. Accepter un non, c'est possible.
+enfant-f|D'accord. Elle dessine avec papa.
+narrateur|Nora joue au cerceau. Clémence n'insiste pas.
+papa|Merci. Tu as su inviter. Tu as su accepter un non.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1495,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Nora dit non. Que fait Clémence ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1668,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Clémence a su inviter. Nora a dit non. Clémence a pu accepter un non. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1835,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Clémence range une craie. Papa lui tend la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2002,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2042,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-10.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-10.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1319,6 +1324,11 @@
 papa|Merci. Tu as su inviter. Tu as su accepter un non.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1502,6 +1512,7 @@
           <t>narrateur|Nora dit non. Que fait Clémence ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1673,6 +1684,7 @@
           <t>narrateur|Clémence a su inviter. Nora a dit non. Clémence a pu accepter un non. Papa est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1840,6 +1852,7 @@
           <t>narrateur|Clémence range une craie. Papa lui tend la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2007,6 +2020,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2025,7 +2039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2049,6 +2063,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2250,6 +2278,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.AMI.001-10.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-10.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Clémence invite Nora aux craies</t>
+          <t>Le soleil de Victorino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Victorino invite Sarah aux craies. Sarah dit non. Victorino accepte et dessine un soleil avec papa.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Clémence est au parc. Papa est au banc. Clémence a des craies. Les craies sont colorées. Nora arrive près du muret. Clémence veut jouer. Tu peux inviter. Inviter, c'est demander. Tu veux jouer avec nous ? Nora secoue la tête. Non. Clémence a le ventre un peu serré. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. D'accord. Elle dessine avec papa. Nora joue au cerceau. Clémence n'insiste pas. Merci. Tu as su inviter. Tu as su accepter un non.</t>
+          <t>Une craie rose a roulé. Elle est sous le banc. Le muret du parc est chaud. Une fourmi marche sur la pierre. Le chapeau de papa est posé. Un peu de poussière blanche brille. Victorino, tu vois la craie ? Oui, papa. Elle est rose. Oui. On la ramasse. En ce moment, Victorino s'accroupit. Il ouvre la boîte. Les craies sont colorées. Il y a du jaune. Oui. Du jaune et du bleu. Sarah arrive près du muret. Elle a un cerceau. Le cerceau tape un peu. Tu peux inviter. Inviter, c'est demander. Inviter, c'est demander. Tu veux jouer avec nous ? Sarah secoue la tête. Non. Victorino a le ventre serré. La craie rose reste dans sa main. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. On accepte un non. D'accord. Victorino reste au muret. Il dessine avec papa. La craie fait un soleil. La poussière colle aux doigts. Tu traces bien. C'est un soleil. Oui. Un soleil jaune. Sarah joue au cerceau. Le cerceau roule. Victorino accepte le non. Merci. Tu as su inviter. Tu as su accepter un non. Elle a dit non. Un non, c'est possible. On finit le soleil ? Oui, papa. La fourmi avance encore. Le muret reste chaud. Tu as fini le soleil ? Oui. Bravo. Tu as fait du bon travail. Victorino pose la craie. Le soleil reste sur la pierre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,65 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Clémence est au parc. Papa est au banc. Clémence a des craies. Les craies sont colorées. Nora arrive près du muret. Clémence veut jouer.
-papa|Tu peux inviter. Inviter, c'est demander.
-enfant-f|Tu veux jouer avec nous ?
-narrateur|Nora secoue la tête.
+          <t>narrateur|Une craie rose a roulé.
+narrateur|Elle est sous le banc.
+narrateur|Le muret du parc est chaud.
+narrateur|Une fourmi marche sur la pierre.
+narrateur|Le chapeau de papa est posé.
+narrateur|Un peu de poussière blanche brille.
+papa|Victorino, tu vois la craie ?
+enfant-m|Oui, papa.
+enfant-m|Elle est rose.
+papa|Oui.
+papa|On la ramasse.
+narrateur|En ce moment, Victorino s'accroupit.
+narrateur|Il ouvre la boîte.
+narrateur|Les craies sont colorées.
+enfant-m|Il y a du jaune.
+papa|Oui.
+papa|Du jaune et du bleu.
+narrateur|Sarah arrive près du muret.
+narrateur|Elle a un cerceau.
+narrateur|Le cerceau tape un peu.
+papa|Tu peux inviter.
+papa|Inviter, c'est demander.
+papa|Inviter, c'est demander.
+enfant-m|Tu veux jouer avec nous ?
+narrateur|Sarah secoue la tête.
 copine|Non.
-narrateur|Clémence a le ventre un peu serré. Papa s'approche.
-papa|On peut accepter un non. Accepter un non, c'est possible.
-enfant-f|D'accord. Elle dessine avec papa.
-narrateur|Nora joue au cerceau. Clémence n'insiste pas.
-papa|Merci. Tu as su inviter. Tu as su accepter un non.</t>
+narrateur|Victorino a le ventre serré.
+narrateur|La craie rose reste dans sa main.
+narrateur|Papa s'approche.
+papa|On peut accepter un non.
+papa|Accepter un non, c'est possible.
+papa|On accepte un non.
+enfant-m|D'accord.
+narrateur|Victorino reste au muret.
+narrateur|Il dessine avec papa.
+narrateur|La craie fait un soleil.
+narrateur|La poussière colle aux doigts.
+papa|Tu traces bien.
+enfant-m|C'est un soleil.
+papa|Oui.
+papa|Un soleil jaune.
+narrateur|Sarah joue au cerceau.
+narrateur|Le cerceau roule.
+narrateur|Victorino accepte le non.
+papa|Merci.
+papa|Tu as su inviter.
+papa|Tu as su accepter un non.
+enfant-m|Elle a dit non.
+papa|Un non, c'est possible.
+papa|On finit le soleil ?
+enfant-m|Oui, papa.
+narrateur|La fourmi avance encore.
+narrateur|Le muret reste chaud.
+papa|Tu as fini le soleil ?
+enfant-m|Oui.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Victorino pose la craie.
+narrateur|Le soleil reste sur la pierre.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1353,7 +1414,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Nora dit non. Que fait Clémence ?</t>
+          <t>Sarah dit non. Que fait Victorino ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1509,10 +1570,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Nora dit non. Que fait Clémence ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Sarah dit non.
+narrateur|Que fait Victorino ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1537,7 +1598,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Clémence a su inviter. Nora a dit non. Clémence a pu accepter un non. Papa est là.</t>
+          <t>Victorino a demandé. C'est inviter. Sarah a dit non. Victorino a accepté le non. Tu as su inviter. Tu as su accepter un non. Bravo, Victorino. D'accord. Oui. Un non, c'est possible. Le soleil jaune est sur le muret. Le cerceau de Sarah roule encore. Tu as fini de dessiner ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1681,10 +1742,22 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Clémence a su inviter. Nora a dit non. Clémence a pu accepter un non. Papa est là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Victorino a demandé.
+narrateur|C'est inviter.
+narrateur|Sarah a dit non.
+narrateur|Victorino a accepté le non.
+papa|Tu as su inviter.
+papa|Tu as su accepter un non.
+papa|Bravo, Victorino.
+enfant-m|D'accord.
+papa|Oui.
+papa|Un non, c'est possible.
+narrateur|Le soleil jaune est sur le muret.
+narrateur|Le cerceau de Sarah roule encore.
+papa|Tu as fini de dessiner ?
+enfant-m|Oui, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1709,7 +1782,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Clémence range une craie. Papa lui tend la main.</t>
+          <t>Victorino range une craie. La poussière colle encore. Je ferme la boîte. Elle fait clic. Oui. On la met dans le sac. Tu prends ma main ? Oui. Ils quittent le muret. Le soleil reste sur la pierre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1849,10 +1922,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Clémence range une craie. Papa lui tend la main.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Victorino range une craie.
+narrateur|La poussière colle encore.
+papa|Je ferme la boîte.
+enfant-m|Elle fait clic.
+papa|Oui.
+papa|On la met dans le sac.
+papa|Tu prends ma main ?
+enfant-m|Oui.
+narrateur|Ils quittent le muret.
+narrateur|Le soleil reste sur la pierre.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1877,7 +1958,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorino a invité. Il a accepté un non. Les craies sont dans la boîte. Bravo, Victorino. On rentre ? Oui. On rentre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2017,10 +2098,16 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Victorino a invité.
+narrateur|Il a accepté un non.
+narrateur|Les craies sont dans la boîte.
+papa|Bravo, Victorino.
+enfant-m|On rentre ?
+papa|Oui.
+papa|On rentre.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2039,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2077,6 +2164,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-10.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-10.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une craie rose a roulé. Elle est sous le banc. Le muret du parc est chaud. Une fourmi marche sur la pierre. Le chapeau de papa est posé. Un peu de poussière blanche brille. Victorino, tu vois la craie ? Oui, papa. Elle est rose. Oui. On la ramasse. En ce moment, Victorino s'accroupit. Il ouvre la boîte. Les craies sont colorées. Il y a du jaune. Oui. Du jaune et du bleu. Sarah arrive près du muret. Elle a un cerceau. Le cerceau tape un peu. Tu peux inviter. Inviter, c'est demander. Inviter, c'est demander. Tu veux jouer avec nous ? Sarah secoue la tête. Non. Victorino a le ventre serré. La craie rose reste dans sa main. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. On accepte un non. D'accord. Victorino reste au muret. Il dessine avec papa. La craie fait un soleil. La poussière colle aux doigts. Tu traces bien. C'est un soleil. Oui. Un soleil jaune. Sarah joue au cerceau. Le cerceau roule. Victorino accepte le non. Merci. Tu as su inviter. Tu as su accepter un non. Elle a dit non. Un non, c'est possible. On finit le soleil ? Oui, papa. La fourmi avance encore. Le muret reste chaud. Tu as fini le soleil ? Oui. Bravo. Tu as fait du bon travail. Victorino pose la craie. Le soleil reste sur la pierre.</t>
+          <t>Une craie rose a roulé. Elle est sous le banc. Le muret du parc est chaud. Une fourmi marche sur la pierre. Le chapeau de papa est posé. Un peu de poussière blanche brille. Victorino, tu vois la craie ? Oui, papa. Elle est rose. Oui. On la ramasse. En ce moment, Victorino s'accroupit. Il ouvre la boîte. Les craies sont colorées. Il y a du jaune. Oui. Du jaune et du bleu. Sarah arrive près du muret. Elle a un cerceau. Le cerceau tape un peu. Tu peux inviter. Inviter, c'est demander. Inviter, c'est demander. Tu veux jouer avec nous ? Sarah secoue la tête. Non. Victorino a le ventre serré. La craie rose reste dans sa main. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. On accepte un non. D'accord. Victorino reste au muret. Il dessine avec papa. La craie fait un soleil. La poussière colle aux doigts. Tu traces bien. C'est un soleil. Oui. Un soleil jaune. Sarah joue au cerceau. Le cerceau roule. Victorino accepte le non. Merci. Tu as su inviter. Tu as su accepter un non. Elle a dit non. Un non, c'est possible. On finit le soleil ? Oui, papa. La fourmi avance encore. Le muret reste chaud. Tu as fini le soleil ? Oui. Bravo. Victorino pose la craie. Le soleil reste sur la pierre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Clémence est au parc. Papa est au banc. Clémence a des craies. Les craies sont colorées. Nora arrive près du muret. Clémence veut jouer. Papa dit : tu peux &lt;emphasis level="moderate"&gt;inviter&lt;/emphasis&gt;. Inviter, c'est demander. Clémence dit : tu veux jouer avec nous ? Nora secoue la tête. Nora dit : non. Clémence a le ventre un peu serré. Papa s'approche. Papa dit : on peut accepter un non. Accepter un non, c'est possible. Clémence dit : d'accord. Elle dessine avec papa. Nora joue au cerceau. Clémence n'insiste pas. Papa dit : merci. Tu as su inviter. Tu as su accepter un non.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une craie rose a roulé. Elle est sous le banc. Le muret du parc est chaud. Une fourmi marche sur la pierre. Le chapeau de papa est posé. Un peu de poussière blanche brille. Victorino, tu vois la craie ? Oui, papa. Elle est rose. Oui. On la ramasse. En ce moment, Victorino s'accroupit. Il ouvre la boîte. Les craies sont colorées. Il y a du jaune. Oui. Du jaune et du bleu. Sarah arrive près du muret. Elle a un cerceau. Le cerceau tape un peu. Tu peux inviter. Inviter, c'est demander. Inviter, c'est demander. Tu veux jouer avec nous ? Sarah secoue la tête. Non. Victorino a le ventre serré. La craie rose reste dans sa main. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. On accepte un non. D'accord. Victorino reste au muret. Il dessine avec papa. La craie fait un soleil. La poussière colle aux doigts. Tu traces bien. C'est un soleil. Oui. Un soleil jaune. Sarah joue au cerceau. Le cerceau roule. Victorino accepte le non. Merci. Tu as su inviter. Tu as su accepter un non. Elle a dit non. Un non, c'est possible. On finit le soleil ? Oui, papa. La fourmi avance encore. Le muret reste chaud. Tu as fini le soleil ? Oui. Bravo. Victorino pose la craie. Le soleil reste sur la pierre.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1380,7 +1380,6 @@
 papa|Tu as fini le soleil ?
 enfant-m|Oui.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 narrateur|Victorino pose la craie.
 narrateur|Le soleil reste sur la pierre.</t>
         </is>
@@ -1419,7 +1418,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nora dit non. Que fait Clémence ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah dit non. Que fait Victorino ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1603,7 +1602,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Clémence a su &lt;emphasis level="moderate"&gt;inviter&lt;/emphasis&gt;. Nora a dit non. Clémence a pu accepter un non. Papa est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino a demandé. C'est inviter. Sarah a dit non. Victorino a accepté le non. Tu as su inviter. Tu as su accepter un non. Bravo, Victorino. D'accord. Oui. Un non, c'est possible. Le soleil jaune est sur le muret. Le cerceau de Sarah roule encore. Tu as fini de dessiner ? Oui, papa.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1787,7 +1786,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Clémence range une craie. Papa lui tend la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino range une craie. La poussière colle encore. Je ferme la boîte. Elle fait clic. Oui. On la met dans le sac. Tu prends ma main ? Oui. Ils quittent le muret. Le soleil reste sur la pierre.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1958,12 +1957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Victorino a invité. Il a accepté un non. Les craies sont dans la boîte. Bravo, Victorino. On rentre ? Oui. On rentre. L'histoire est finie.</t>
+          <t>Victorino a invité. Il a accepté un non. Les craies sont dans la boîte. Bravo, Victorino. On rentre ? Oui. On rentre.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino a invité. Il a accepté un non. Les craies sont dans la boîte. Bravo, Victorino. On rentre ? Oui. On rentre.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2104,8 +2103,7 @@
 papa|Bravo, Victorino.
 enfant-m|On rentre ?
 papa|Oui.
-papa|On rentre.
-narrateur|L'histoire est finie.</t>
+papa|On rentre.</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2171,6 +2169,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-10.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-10.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Clémence, Nora, papa</t>
+          <t>Victorino, Sarah, papa</t>
         </is>
       </c>
     </row>
